--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>5636468000</v>
+        <v>-4461960000</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -770,11 +770,11 @@
         </is>
       </c>
       <c r="L8" s="6" t="n">
-        <v>4.78039</v>
+        <v>-3.415216</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -848,11 +848,11 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>2383134393000</v>
+        <v>2745684710000</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -926,11 +926,11 @@
         </is>
       </c>
       <c r="L10" s="6" t="n">
-        <v>14.452181</v>
+        <v>16.528512</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1004,11 +1004,11 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>3346413772000</v>
+        <v>3498567430000</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1082,11 +1082,11 @@
         </is>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-963279379000</v>
+        <v>-752882719000</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1160,11 +1160,11 @@
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>-5.841671</v>
+        <v>-4.532214</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1238,11 +1238,11 @@
         </is>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-834225780000</v>
+        <v>-752269407000</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1316,11 +1316,11 @@
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>-5.059044</v>
+        <v>-4.528522</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1352,27 +1352,27 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>GGXWDG</t>
+          <t>GGX_NGDP</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Gross debt, General government, Domestic currency</t>
+          <t>Expenditure, General government, Percent of GDP</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Gross debt is the sum of all liabilities that are debt instruments.  Debt instruments are financial instruments that require the payment of principal and/or interest at some point(s) in the future. Debt instruments consist of SDRs, currency and deposits, debt securities, loans, insurance technical reserves, pension and related entitlements, provision for calls under standardized guarantees, and other accounts receivable/payable.  Central, state, and local governments, including their agencies and departments. Currency issued by the country of origin, used internally. Used to specify what Unit of Measure the country used to provide data to the IMF.�</t>
+          <t>Expenditure refers to the total outflow of resources, including payments, purchases, and transfers, made by a government entity during a specific period to fulfill its various functions and obligations. It encompasses spending on goods and services, wages and salaries, social benefits, debt servicing, infrastructure investments, and other government programs and activities. Expenditure represents the utilization of government funds to provide public services, maintain infrastructure, implement policies, and meet financial obligations. Monitoring expenditure patterns and allocations provides insight into government priorities, policy objectives, and fiscal sustainability.  Central, state, and local governments, including their agencies and departments. Value expressed as a percent of the Gross Domestic Product (GDP) of a country. A ratio expressed as a fraction of 100.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domestic currency</t>
+          <t>Percent</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1381,11 +1381,11 @@
         </is>
       </c>
       <c r="I16" s="5" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n">
-        <v>50911791035000</v>
+      <c r="L16" s="6" t="n">
+        <v>21.060726</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1430,27 +1430,23 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>GGXWDG_NGDP</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Gross debt, General government, Percent of GDP</t>
+          <t>Population, Persons for countries / Index for country groups</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Gross debt is the sum of all liabilities that are debt instruments.  Debt instruments are financial instruments that require the payment of principal and/or interest at some point(s) in the future. Debt instruments consist of SDRs, currency and deposits, debt securities, loans, insurance technical reserves, pension and related entitlements, provision for calls under standardized guarantees, and other accounts receivable/payable.  Central, state, and local governments, including their agencies and departments. Value expressed as a percent of the Gross Domestic Product (GDP) of a country. A ratio expressed as a fraction of 100.</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
+          <t>The total number of people living in a specific area or country. Persons for countries / Index for country groups</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1459,24 +1455,24 @@
         </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>308.747344</v>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>28516896</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1508,24 +1504,20 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>GGX_NGDP</t>
+          <t>LUR</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Expenditure, General government, Percent of GDP</t>
+          <t>Unemployment rate</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Expenditure refers to the total outflow of resources, including payments, purchases, and transfers, made by a government entity during a specific period to fulfill its various functions and obligations. It encompasses spending on goods and services, wages and salaries, social benefits, debt servicing, infrastructure investments, and other government programs and activities. Expenditure represents the utilization of government funds to provide public services, maintain infrastructure, implement policies, and meet financial obligations. Monitoring expenditure patterns and allocations provides insight into government priorities, policy objectives, and fiscal sustainability.  Central, state, and local governments, including their agencies and departments. Value expressed as a percent of the Gross Domestic Product (GDP) of a country. A ratio expressed as a fraction of 100.</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
+          <t>The percentage of the labor force that is unemployed and actively seeking employment. It is calculated as the number of unemployed persons divided by the total labor force. A measure that expresses the frequency of occurrence of an event or phenomenon in relation to another quantity.</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1537,24 +1529,24 @@
         </is>
       </c>
       <c r="I18" s="5" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="L18" s="6" t="n">
-        <v>20.293852</v>
+        <v>5.468</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1586,23 +1578,27 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>NGDP</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Population, Persons for countries / Index for country groups</t>
+          <t>Gross domestic product (GDP), Current prices, Domestic currency</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>The total number of people living in a specific area or country. Persons for countries / Index for country groups</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes Currency issued by the country of origin, used internally. Used to specify what Unit of Measure the country used to provide data to the IMF.�</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Domestic currency</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1611,11 +1607,11 @@
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1624,11 +1620,11 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>27102199</v>
+        <v>294678468053000</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1660,23 +1656,27 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>LUR</t>
+          <t>NGDPD</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Unemployment rate</t>
+          <t>Gross domestic product (GDP), Current prices, US dollar</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>The percentage of the labor force that is unemployed and actively seeking employment. It is calculated as the number of unemployed persons divided by the total labor force. A measure that expresses the frequency of occurrence of an event or phenomenon in relation to another quantity.</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>US dollar</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1685,24 +1685,24 @@
         </is>
       </c>
       <c r="I20" s="5" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>35.553745</v>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>130649428000</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1734,27 +1734,27 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>NGDP</t>
+          <t>NGDPDPC</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Current prices, Domestic currency</t>
+          <t>Gross domestic product (GDP), Current prices, Per capita, US dollar</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes Currency issued by the country of origin, used internally. Used to specify what Unit of Measure the country used to provide data to the IMF.�</t>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes Per capita is a Latin term that means "for each head" or "per person." It is often used in economic and statistical analysis to compare data across populations of different sizes. When a figure is given per capita, it means the average amount per person. For example, GDP per capita is a measure of a country's economic output per person.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Domestic currency</t>
+          <t>US dollar</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1775,12 +1775,12 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
-        <v>184820483420000</v>
+      <c r="L21" s="6" t="n">
+        <v>4581.474382</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1812,27 +1812,27 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>NGDPD</t>
+          <t>NGDPPC</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Current prices, US dollar</t>
+          <t>Gross domestic product (GDP), Current prices, Per capita, Domestic currency</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes</t>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes Per capita is a Latin term that means "for each head" or "per person." It is often used in economic and statistical analysis to compare data across populations of different sizes. When a figure is given per capita, it means the average amount per person. For example, GDP per capita is a measure of a country's economic output per person. Currency issued by the country of origin, used internally. Used to specify what Unit of Measure the country used to provide data to the IMF.�</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>US dollar</t>
+          <t>Domestic currency</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1841,11 +1841,11 @@
         </is>
       </c>
       <c r="I22" s="5" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -1853,12 +1853,12 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n">
-        <v>117908128000</v>
+      <c r="L22" s="6" t="n">
+        <v>10333469.254598</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -1890,24 +1890,20 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>NGDPDPC</t>
+          <t>NGDPRPPPPC</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Current prices, Per capita, US dollar</t>
+          <t>Gross domestic product (GDP), Constant prices, Per capita, purchasing power parity (PPP) international dollar, ICP benchmark 2021</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes Per capita is a Latin term that means "for each head" or "per person." It is often used in economic and statistical analysis to compare data across populations of different sizes. When a figure is given per capita, it means the average amount per person. For example, GDP per capita is a measure of a country's economic output per person.</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>US dollar</t>
-        </is>
-      </c>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values that have had the effect of price changes removed, expressed as time series in constant prices (fixed base) or chain-linked volume terms, or as non-time series in previous year's prices Average income or economic output per person adjusted for cost-of-living differences between countries, expressed in international dollars. ICP benchmark 2021</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1932,11 +1928,11 @@
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4350.500451</v>
+        <v>8763.950225000001</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -1968,22 +1964,22 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>NGDPPC</t>
+          <t>NGDP_D</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Current prices, Per capita, Domestic currency</t>
+          <t>Gross domestic product (GDP), Price deflator, Index</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes Per capita is a Latin term that means "for each head" or "per person." It is often used in economic and statistical analysis to compare data across populations of different sizes. When a figure is given per capita, it means the average amount per person. For example, GDP per capita is a measure of a country's economic output per person. Currency issued by the country of origin, used internally. Used to specify what Unit of Measure the country used to provide data to the IMF.�</t>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  An economic indicator used to adjust nominal economic data series for changes in relevant price levels.  Price deflators can be explicit, such as producer or consumer price indices, or implicit, such as the GDP deflator derived by dividing nominal GDP by GDP in volume terms. A statistical measure that expresses the relative change in a variable over time.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domestic currency</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1997,11 +1993,11 @@
         </is>
       </c>
       <c r="I24" s="5" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2009,12 +2005,12 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L24" s="6" t="n">
-        <v>6819390.752229</v>
+      <c r="L24" s="5" t="n">
+        <v>1.371581655493518e+16</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2046,23 +2042,27 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>NGDPRPPPPC</t>
+          <t>NGDP_FY</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Constant prices, Per capita, purchasing power parity (PPP) international dollar, ICP benchmark 2021</t>
+          <t>Gross domestic product (GDP), Current prices, Fiscal year, Domestic currency</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values that have had the effect of price changes removed, expressed as time series in constant prices (fixed base) or chain-linked volume terms, or as non-time series in previous year's prices Average income or economic output per person adjusted for cost-of-living differences between countries, expressed in international dollars. ICP benchmark 2021</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes A 12-month period that a company or government uses for accounting purposes. The fiscal year may or may not align with the calendar year. For example, a company's fiscal year could start on July 1st and end on June 30th of the following year. Currency issued by the country of origin, used internally. Used to specify what Unit of Measure the country used to provide data to the IMF.�</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Domestic currency</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2071,11 +2071,11 @@
         </is>
       </c>
       <c r="I25" s="5" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2083,12 +2083,12 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L25" s="6" t="n">
-        <v>8261.804599999999</v>
+      <c r="L25" s="5" t="n">
+        <v>294678468053000</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>NGDP_D</t>
+          <t>NGDP_RPCH</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Price deflator, Index</t>
+          <t>Gross domestic product (GDP), Constant prices, Percent change</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  An economic indicator used to adjust nominal economic data series for changes in relevant price levels.  Price deflators can be explicit, such as producer or consumer price indices, or implicit, such as the GDP deflator derived by dividing nominal GDP by GDP in volume terms. A statistical measure that expresses the relative change in a variable over time.</t>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values that have had the effect of price changes removed, expressed as time series in constant prices (fixed base) or chain-linked volume terms, or as non-time series in previous year's prices This measures the relative change in a value over time, expressed as a percentage. It is calculated as the difference between the new value and the old value, divided by the old value, and multiplied by 100. 1 A ratio expressed as a fraction of 100.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Percent</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -2161,12 +2161,12 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n">
-        <v>8.658552989844166e+16</v>
+      <c r="L26" s="6" t="n">
+        <v>7.046874</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2198,27 +2198,27 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>NGDP_FY</t>
+          <t>NGSD_NGDP</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Current prices, Fiscal year, Domestic currency</t>
+          <t>Gross national savings, Percent of GDP</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes A 12-month period that a company or government uses for accounting purposes. The fiscal year may or may not align with the calendar year. For example, a company's fiscal year could start on July 1st and end on June 30th of the following year. Currency issued by the country of origin, used internally. Used to specify what Unit of Measure the country used to provide data to the IMF.�</t>
+          <t>Gross national saving represents the total amount of income earned by residents of an economic territory (including households, nonprofit institutions serving housholds, corporations, government entities) that is not consumed during a specific period.  Value expressed as a percent of the Gross Domestic Product (GDP) of a country. A ratio expressed as a fraction of 100.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Domestic currency</t>
+          <t>Percent</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2227,24 +2227,24 @@
         </is>
       </c>
       <c r="I27" s="5" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>184820483420000</v>
+      <c r="L27" s="6" t="n">
+        <v>36.002376</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>NGDP_RPCH</t>
+          <t>NID_NGDP</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Constant prices, Percent change</t>
+          <t>Gross capital formation, Percent of GDP</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values that have had the effect of price changes removed, expressed as time series in constant prices (fixed base) or chain-linked volume terms, or as non-time series in previous year's prices This measures the relative change in a value over time, expressed as a percentage. It is calculated as the difference between the new value and the old value, divided by the old value, and multiplied by 100. 1 A ratio expressed as a fraction of 100.</t>
+          <t>Acquisitions less disposals of produced assets for purposes of fixed capital formation, inventories or valuables. Value expressed as a percent of the Gross Domestic Product (GDP) of a country. A ratio expressed as a fraction of 100.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I28" s="5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -2314,15 +2314,15 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="L28" s="6" t="n">
-        <v>5.9972</v>
+        <v>28.561106</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>NGSD_NGDP</t>
+          <t>PCPI</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Gross national savings, Percent of GDP</t>
+          <t>All Items, Consumer price index (CPI), Period average</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Gross national saving represents the total amount of income earned by residents of an economic territory (including households, nonprofit institutions serving housholds, corporations, government entities) that is not consumed during a specific period.  Value expressed as a percent of the Gross Domestic Product (GDP) of a country. A ratio expressed as a fraction of 100.</t>
+          <t>All items in the context of the consumer price index indicates that the index includes prices for all items included in the consumer price index basket.  This includes prices related to food, beverages, clothing, housing, health, transport, communications, recreation, education, restaurants and hotels and other miscellanoues goods and services. The Consumer Price Index (CPI) is an index of the prices of consumption goods and services, as compared to a certain reference period. This refers to the arithmetic mean (average) value of a data series calculated over a specified period, such as a month, quarter, or year. It provides a representative value for the entire period, smoothing out any short-term fluctuations. A statistical measure that expresses the relative change in a variable over time.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Percent</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="I29" s="5" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2392,15 +2392,15 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>12.624055</v>
+        <v>15002708388228.5</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>NID_NGDP</t>
+          <t>PCPIE</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Gross capital formation, Percent of GDP</t>
+          <t>All Items, Consumer price index (CPI), End-of-period (EoP)</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Acquisitions less disposals of produced assets for purposes of fixed capital formation, inventories or valuables. Value expressed as a percent of the Gross Domestic Product (GDP) of a country. A ratio expressed as a fraction of 100.</t>
+          <t>All items in the context of the consumer price index indicates that the index includes prices for all items included in the consumer price index basket.  This includes prices related to food, beverages, clothing, housing, health, transport, communications, recreation, education, restaurants and hotels and other miscellanoues goods and services. The Consumer Price Index (CPI) is an index of the prices of consumption goods and services, as compared to a certain reference period. Refers to the end of any specific period, such as a quarter, month, or week. It marks the point at which economic or financial data or indexes are aggregated and/or analyzed. A statistical measure that expresses the relative change in a variable over time.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Percent</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2461,24 +2461,24 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L30" s="6" t="n">
-        <v>5.111249</v>
+        <v>21433099276217.2</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2510,22 +2510,22 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>PCPI</t>
+          <t>PCPIEPCH</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>All Items, Consumer price index (CPI), Period average</t>
+          <t>All Items, Consumer price index (CPI), End-of-period (EoP), percent change</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>All items in the context of the consumer price index indicates that the index includes prices for all items included in the consumer price index basket.  This includes prices related to food, beverages, clothing, housing, health, transport, communications, recreation, education, restaurants and hotels and other miscellanoues goods and services. The Consumer Price Index (CPI) is an index of the prices of consumption goods and services, as compared to a certain reference period. This refers to the arithmetic mean (average) value of a data series calculated over a specified period, such as a month, quarter, or year. It provides a representative value for the entire period, smoothing out any short-term fluctuations. A statistical measure that expresses the relative change in a variable over time.</t>
+          <t>All items in the context of the consumer price index indicates that the index includes prices for all items included in the consumer price index basket.  This includes prices related to food, beverages, clothing, housing, health, transport, communications, recreation, education, restaurants and hotels and other miscellanoues goods and services. The Consumer Price Index (CPI) is an index of the prices of consumption goods and services, as compared to a certain reference period. This focuses on the change between the value at the beginning of a period and the value at the end of that period. The period could be a day, month, quarter, year, etc. This is often used to track changes in financial or economic indicators over specific periods. A ratio expressed as a fraction of 100.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Percent</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -2539,11 +2539,11 @@
         </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -2552,11 +2552,11 @@
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>9111677627913.15</v>
+        <v>139.829126</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2588,22 +2588,22 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>PCPIE</t>
+          <t>PCPIPCH</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>All Items, Consumer price index (CPI), End-of-period (EoP)</t>
+          <t>All Items, Consumer price index (CPI), Period average, percent change</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>All items in the context of the consumer price index indicates that the index includes prices for all items included in the consumer price index basket.  This includes prices related to food, beverages, clothing, housing, health, transport, communications, recreation, education, restaurants and hotels and other miscellanoues goods and services. The Consumer Price Index (CPI) is an index of the prices of consumption goods and services, as compared to a certain reference period. Refers to the end of any specific period, such as a quarter, month, or week. It marks the point at which economic or financial data or indexes are aggregated and/or analyzed. A statistical measure that expresses the relative change in a variable over time.</t>
+          <t>All items in the context of the consumer price index indicates that the index includes prices for all items included in the consumer price index basket.  This includes prices related to food, beverages, clothing, housing, health, transport, communications, recreation, education, restaurants and hotels and other miscellanoues goods and services. The Consumer Price Index (CPI) is an index of the prices of consumption goods and services, as compared to a certain reference period. This calculates the change relative to the average value over the entire period, not just the starting point. This is often used when the data fluctuates significantly within the period, and the average provides a more representative value for comparison. A ratio expressed as a fraction of 100.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Percent</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -2630,11 +2630,11 @@
         </is>
       </c>
       <c r="L32" s="6" t="n">
-        <v>11748900163963.3</v>
+        <v>174.693839</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2666,24 +2666,20 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>PCPIEPCH</t>
+          <t>PPPEX</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>All Items, Consumer price index (CPI), End-of-period (EoP), percent change</t>
+          <t>Rate, Domestic currency per international dollar in PPP terms, ICP benchmarks 2017-2021</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>All items in the context of the consumer price index indicates that the index includes prices for all items included in the consumer price index basket.  This includes prices related to food, beverages, clothing, housing, health, transport, communications, recreation, education, restaurants and hotels and other miscellanoues goods and services. The Consumer Price Index (CPI) is an index of the prices of consumption goods and services, as compared to a certain reference period. This focuses on the change between the value at the beginning of a period and the value at the end of that period. The period could be a day, month, quarter, year, etc. This is often used to track changes in financial or economic indicators over specific periods. A ratio expressed as a fraction of 100.</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
+          <t>A measure that expresses the frequency of occurrence of an event or phenomenon in relation to another quantity. Purchasing power parities (PPPs) are the rates of currency conversion that try to equalize the purchasing power of different currencies, by eliminating the differences in price levels between countries. ICP benchmarks 2017-2021</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr">
         <is>
           <t>0</t>
@@ -2695,11 +2691,11 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -2708,11 +2704,11 @@
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>79.585633</v>
+        <v>945.1611329999999</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -2744,27 +2740,23 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>PCPIPCH</t>
+          <t>PPPGDP</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>All Items, Consumer price index (CPI), Period average, percent change</t>
+          <t>Gross domestic product (GDP), Current prices, Purchasing power parity (PPP) international dollar, ICP benchmarks 2017-2021</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>All items in the context of the consumer price index indicates that the index includes prices for all items included in the consumer price index basket.  This includes prices related to food, beverages, clothing, housing, health, transport, communications, recreation, education, restaurants and hotels and other miscellanoues goods and services. The Consumer Price Index (CPI) is an index of the prices of consumption goods and services, as compared to a certain reference period. This calculates the change relative to the average value over the entire period, not just the starting point. This is often used when the data fluctuates significantly within the period, and the average provides a more representative value for comparison. A ratio expressed as a fraction of 100.</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes Rates of currency conversion that equalize purchasing power by eliminating price level differences between countries. ICP benchmarks 2017-2021</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2785,12 +2777,12 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L34" s="6" t="n">
-        <v>94.37248</v>
+      <c r="L34" s="5" t="n">
+        <v>311775906000</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -2822,17 +2814,17 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>PPPEX</t>
+          <t>PPPPC</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Rate, Domestic currency per international dollar in PPP terms, ICP benchmarks 2017-2021</t>
+          <t>Gross domestic product (GDP), Per capita, purchasing power parity (PPP) international dollar, ICP benchmarks 2017-2021</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>A measure that expresses the frequency of occurrence of an event or phenomenon in relation to another quantity. Purchasing power parities (PPPs) are the rates of currency conversion that try to equalize the purchasing power of different currencies, by eliminating the differences in price levels between countries. ICP benchmarks 2017-2021</t>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Average income or economic output per person adjusted for cost-of-living differences between countries, expressed in international dollars. ICP benchmarks 2017-2021</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
@@ -2847,11 +2839,11 @@
         </is>
       </c>
       <c r="I35" s="5" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -2860,11 +2852,11 @@
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>670.73838</v>
+        <v>10933.023904</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -2896,23 +2888,27 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>PPPGDP</t>
+          <t>PPPSH</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Current prices, Purchasing power parity (PPP) international dollar, ICP benchmarks 2017-2021</t>
+          <t>Gross domestic product (GDP), Purchasing power parity (PPP) international dollar, percent of world GDP, Percent, ICP benchmarks 2017-2021</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Values expressed without any adjustment for price changes Rates of currency conversion that equalize purchasing power by eliminating price level differences between countries. ICP benchmarks 2017-2021</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
+          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Share of global GDP attributed to a country, adjusted for purchasing power parity. A ratio expressed as a fraction of 100. ICP benchmarks 2017-2021</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2933,12 +2929,12 @@
           <t>2027</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n">
-        <v>275547798000</v>
+      <c r="L36" s="6" t="n">
+        <v>0.130377</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -2970,20 +2966,24 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>PPPPC</t>
+          <t>TMG_RPCH</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Per capita, purchasing power parity (PPP) international dollar, ICP benchmarks 2017-2021</t>
+          <t>Imports of goods, Volume, Cost insurance freight (CIF), Percent change</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Average income or economic output per person adjusted for cost-of-living differences between countries, expressed in international dollars. ICP benchmarks 2017-2021</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr"/>
+          <t>Imports of goods reflects the change in the economic ownership of goods from non-residents to residents of the compiling economy, irrespective of physical movement of goods across national borders. The quantity of goods or services produced or traded, often measured in terms of physical units or monetary value. The c.i.f. price (i.e. cost, insurance and freight price) is the price of a good delivered at the frontier of the importing country, including any insurance and freight charges incurred to that point, or the price of a service delivered to a resident, before the payment of any import duties or other taxes on imports or trade and transport margins within the country.  This measures the relative change in a value over time, expressed as a percentage. It is calculated as the difference between the new value and the old value, divided by the old value, and multiplied by 100. 1 A ratio expressed as a fraction of 100.</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
           <t>0</t>
@@ -2995,11 +2995,11 @@
         </is>
       </c>
       <c r="I37" s="5" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -3008,11 +3008,11 @@
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>10166.990517</v>
+        <v>5.869188</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>PPPSH</t>
+          <t>TM_RPCH</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product (GDP), Purchasing power parity (PPP) international dollar, percent of world GDP, Percent, ICP benchmarks 2017-2021</t>
+          <t>Imports of goods and services, Volume, Cost insurance freight (CIF), Percent change</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Gross domestic product reflects the total income earned through the production of goods and services in an economic territory during an accounting period. It can be measured in three different ways: using either the expenditure approach, the income approach, or the production approach.  Share of global GDP attributed to a country, adjusted for purchasing power parity. A ratio expressed as a fraction of 100. ICP benchmarks 2017-2021</t>
+          <t>Imports of goods and services reflect the change in the economic ownership of goods from non-residents to residents of the compiling economy, irrespective of physical movement of goods across national borders. Imports of services reflect services provided by non-residents to residents The quantity of goods or services produced or traded, often measured in terms of physical units or monetary value. The c.i.f. price (i.e. cost, insurance and freight price) is the price of a good delivered at the frontier of the importing country, including any insurance and freight charges incurred to that point, or the price of a service delivered to a resident, before the payment of any import duties or other taxes on imports or trade and transport margins within the country.  This measures the relative change in a value over time, expressed as a percentage. It is calculated as the difference between the new value and the old value, divided by the old value, and multiplied by 100. 1 A ratio expressed as a fraction of 100.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3073,11 +3073,11 @@
         </is>
       </c>
       <c r="I38" s="5" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -3086,11 +3086,11 @@
         </is>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.117296</v>
+        <v>6.270845</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3122,17 +3122,17 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>TMG_RPCH</t>
+          <t>TXG_RPCH</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Imports of goods, Volume, Cost insurance freight (CIF), Percent change</t>
+          <t>Exports of goods, Volume, Free on board (FOB), Percent change</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Imports of goods reflects the change in the economic ownership of goods from non-residents to residents of the compiling economy, irrespective of physical movement of goods across national borders. The quantity of goods or services produced or traded, often measured in terms of physical units or monetary value. The c.i.f. price (i.e. cost, insurance and freight price) is the price of a good delivered at the frontier of the importing country, including any insurance and freight charges incurred to that point, or the price of a service delivered to a resident, before the payment of any import duties or other taxes on imports or trade and transport margins within the country.  This measures the relative change in a value over time, expressed as a percentage. It is calculated as the difference between the new value and the old value, divided by the old value, and multiplied by 100. 1 A ratio expressed as a fraction of 100.</t>
+          <t>Exports of goods reflects the change in the economic ownership of goods from residents of the compiling economy to non-residents, irrespective of physical movement of goods across national borders. The quantity of goods or services produced or traded, often measured in terms of physical units or monetary value. The f.o.b. price (free on board price) of exports and imports of goods is the market value of the goods at the point of uniform valuation, (the customs frontier of the economy from which they are exported).  It is equal to the c.i.f. price less the costs of transportation and insurance charges, between the customs frontier of the exporting (importing) country and that of the importing (exporting) country. This measures the relative change in a value over time, expressed as a percentage. It is calculated as the difference between the new value and the old value, divided by the old value, and multiplied by 100. 1 A ratio expressed as a fraction of 100.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3151,11 +3151,11 @@
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -3164,11 +3164,11 @@
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>10.051507</v>
+        <v>10.853228</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>TM_RPCH</t>
+          <t>TX_RPCH</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Imports of goods and services, Volume, Cost insurance freight (CIF), Percent change</t>
+          <t>Exports of goods and services, Volume, Free on board (FOB), Percent change</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Imports of goods and services reflect the change in the economic ownership of goods from non-residents to residents of the compiling economy, irrespective of physical movement of goods across national borders. Imports of services reflect services provided by non-residents to residents The quantity of goods or services produced or traded, often measured in terms of physical units or monetary value. The c.i.f. price (i.e. cost, insurance and freight price) is the price of a good delivered at the frontier of the importing country, including any insurance and freight charges incurred to that point, or the price of a service delivered to a resident, before the payment of any import duties or other taxes on imports or trade and transport margins within the country.  This measures the relative change in a value over time, expressed as a percentage. It is calculated as the difference between the new value and the old value, divided by the old value, and multiplied by 100. 1 A ratio expressed as a fraction of 100.</t>
+          <t>Exports of goods and services reflect the export of goods reflect changes in the economic ownership of goods from residents of the compiling economy to non-residents, irrespective of physical movement of goods across national borders. Exports of services provided by residents to non-residents. The quantity of goods or services produced or traded, often measured in terms of physical units or monetary value. The f.o.b. price (free on board price) of exports and imports of goods is the market value of the goods at the point of uniform valuation, (the customs frontier of the economy from which they are exported).  It is equal to the c.i.f. price less the costs of transportation and insurance charges, between the customs frontier of the exporting (importing) country and that of the importing (exporting) country. This measures the relative change in a value over time, expressed as a percentage. It is calculated as the difference between the new value and the old value, divided by the old value, and multiplied by 100. 1 A ratio expressed as a fraction of 100.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -3229,11 +3229,11 @@
         </is>
       </c>
       <c r="I40" s="5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -3242,11 +3242,11 @@
         </is>
       </c>
       <c r="L40" s="6" t="n">
-        <v>6.681715</v>
+        <v>10.167712</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3260,162 +3260,6 @@
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/imf/excel/ove_fmi_weo_venezuela.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>FMI - World Economic Outlook</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>TXG_RPCH</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Exports of goods, Volume, Free on board (FOB), Percent change</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Exports of goods reflects the change in the economic ownership of goods from residents of the compiling economy to non-residents, irrespective of physical movement of goods across national borders. The quantity of goods or services produced or traded, often measured in terms of physical units or monetary value. The f.o.b. price (free on board price) of exports and imports of goods is the market value of the goods at the point of uniform valuation, (the customs frontier of the economy from which they are exported).  It is equal to the c.i.f. price less the costs of transportation and insurance charges, between the customs frontier of the exporting (importing) country and that of the importing (exporting) country. This measures the relative change in a value over time, expressed as a percentage. It is calculated as the difference between the new value and the old value, divided by the old value, and multiplied by 100. 1 A ratio expressed as a fraction of 100.</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="L41" s="6" t="n">
-        <v>-0.907603</v>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>9/16/2025</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/imf/csv/ove_fmi_weo_venezuela.csv</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/imf/json/ove_fmi_weo_venezuela.json</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/imf/excel/ove_fmi_weo_venezuela.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>FMI - World Economic Outlook</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>TX_RPCH</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Exports of goods and services, Volume, Free on board (FOB), Percent change</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Exports of goods and services reflect the export of goods reflect changes in the economic ownership of goods from residents of the compiling economy to non-residents, irrespective of physical movement of goods across national borders. Exports of services provided by residents to non-residents. The quantity of goods or services produced or traded, often measured in terms of physical units or monetary value. The f.o.b. price (free on board price) of exports and imports of goods is the market value of the goods at the point of uniform valuation, (the customs frontier of the economy from which they are exported).  It is equal to the c.i.f. price less the costs of transportation and insurance charges, between the customs frontier of the exporting (importing) country and that of the importing (exporting) country. This measures the relative change in a value over time, expressed as a percentage. It is calculated as the difference between the new value and the old value, divided by the old value, and multiplied by 100. 1 A ratio expressed as a fraction of 100.</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="L42" s="6" t="n">
-        <v>-1.160338</v>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>9/16/2025</t>
-        </is>
-      </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/imf/csv/ove_fmi_weo_venezuela.csv</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>assets/data/imf/json/ove_fmi_weo_venezuela.json</t>
-        </is>
-      </c>
-      <c r="P42" s="4" t="inlineStr">
         <is>
           <t>assets/data/imf/excel/ove_fmi_weo_venezuela.xlsx</t>
         </is>
@@ -3501,7 +3345,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3380,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -3546,7 +3390,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1253</v>
+        <v>1216</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
+++ b/assets/data/imf/catalog/catalogo_dataset_web_ove_fmi_weo.xlsx
@@ -3345,7 +3345,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
